--- a/reports/hazop_system_45.xlsx
+++ b/reports/hazop_system_45.xlsx
@@ -468,7 +468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HAZOP preparation — System 45</t>
+          <t>HAZOP preparation — System 45 (functional loops)</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>45-XV4806, 45-XV4806, 45-XY4806, 45-XY4806A, 45-XY4806B, 45-ZL4806, 45-ZS4806</t>
+          <t>45-XV4806, 45-XY4806, 45-XY4806A, 45-XY4806B, 45-ZL4806, 45-ZS4806</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -662,16 +662,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,15 +714,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -743,12 +761,15 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>45-XV4804</t>
+          <t>45-XV4804 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -772,12 +793,15 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>45-XV4804</t>
+          <t>45-XV4804 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -794,16 +818,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -843,15 +870,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -875,12 +917,15 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>45-XV4805</t>
+          <t>45-XV4805 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -904,12 +949,15 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>45-XV4805</t>
+          <t>45-XV4805 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -926,16 +974,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -948,7 +999,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 45-XV4806, 45-XV4806, 45-XY4806, 45-XY4806A, 45-XY4806B, 45-ZL4806, 45-ZS4806</t>
+          <t>Members: 45-XV4806, 45-XY4806, 45-XY4806A, 45-XY4806B, 45-ZL4806, 45-ZS4806</t>
         </is>
       </c>
     </row>
@@ -975,15 +1026,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1007,12 +1073,15 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>45-XV4806</t>
+          <t>45-XV4806 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1036,12 +1105,15 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>45-XV4806</t>
+          <t>45-XV4806 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1065,12 +1137,15 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>45-XV4806</t>
+          <t>45-XV4806 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1094,12 +1169,15 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>45-XV4806</t>
+          <t>45-XV4806 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1116,16 +1194,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,15 +1246,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1202,7 +1298,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1231,7 +1330,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1260,7 +1362,10 @@
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1289,7 +1394,10 @@
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1318,7 +1426,10 @@
       </c>
       <c r="E8" s="6" t="inlineStr"/>
       <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1347,7 +1458,10 @@
       </c>
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1376,7 +1490,10 @@
       </c>
       <c r="E10" s="6" t="inlineStr"/>
       <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1405,7 +1522,10 @@
       </c>
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1422,16 +1542,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1471,15 +1594,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1508,7 +1646,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1537,7 +1678,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
